--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -40898,6 +40898,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1763">
+      <c r="A1763" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1763" t="n">
+        <v>20010</v>
+      </c>
+      <c r="C1763" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D1763" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="E1763" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F1763" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G1763" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -40921,6 +40921,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1764">
+      <c r="A1764" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1764" t="n">
+        <v>33260</v>
+      </c>
+      <c r="C1764" t="n">
+        <v>1.24500000476837</v>
+      </c>
+      <c r="D1764" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E1764" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="F1764" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G1764" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -40944,6 +40944,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1765">
+      <c r="A1765" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1765" t="n">
+        <v>26231</v>
+      </c>
+      <c r="C1765" t="n">
+        <v>1.24500000476837</v>
+      </c>
+      <c r="D1765" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="E1765" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="F1765" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G1765" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -40967,6 +40967,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1766">
+      <c r="A1766" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1766" t="n">
+        <v>10015</v>
+      </c>
+      <c r="C1766" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="D1766" t="n">
+        <v>1.20500004291534</v>
+      </c>
+      <c r="E1766" t="n">
+        <v>1.20500004291534</v>
+      </c>
+      <c r="F1766" t="n">
+        <v>1.23500001430511</v>
+      </c>
+      <c r="G1766" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -40808,19 +40808,19 @@
     </row>
     <row r="1759">
       <c r="A1759" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1759" t="n">
-        <v>20988</v>
+        <v>39223</v>
       </c>
       <c r="C1759" t="n">
         <v>1.26499998569489</v>
       </c>
       <c r="D1759" t="n">
-        <v>1.24500000476837</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="E1759" t="n">
-        <v>1.26499998569489</v>
+        <v>1.25999999046326</v>
       </c>
       <c r="F1759" t="n">
         <v>1.25999999046326</v>
@@ -40831,22 +40831,22 @@
     </row>
     <row r="1760">
       <c r="A1760" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1760" t="n">
-        <v>15821</v>
+        <v>20988</v>
       </c>
       <c r="C1760" t="n">
+        <v>1.26499998569489</v>
+      </c>
+      <c r="D1760" t="n">
+        <v>1.24500000476837</v>
+      </c>
+      <c r="E1760" t="n">
+        <v>1.26499998569489</v>
+      </c>
+      <c r="F1760" t="n">
         <v>1.25999999046326</v>
-      </c>
-      <c r="D1760" t="n">
-        <v>1.22500002384186</v>
-      </c>
-      <c r="E1760" t="n">
-        <v>1.24500000476837</v>
-      </c>
-      <c r="F1760" t="n">
-        <v>1.24000000953674</v>
       </c>
       <c r="G1760" t="s">
         <v>7</v>
@@ -40854,19 +40854,19 @@
     </row>
     <row r="1761">
       <c r="A1761" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1761" t="n">
-        <v>5642</v>
+        <v>15821</v>
       </c>
       <c r="C1761" t="n">
         <v>1.25999999046326</v>
       </c>
       <c r="D1761" t="n">
-        <v>1.24000000953674</v>
+        <v>1.22500002384186</v>
       </c>
       <c r="E1761" t="n">
-        <v>1.25</v>
+        <v>1.24500000476837</v>
       </c>
       <c r="F1761" t="n">
         <v>1.24000000953674</v>
@@ -40877,19 +40877,19 @@
     </row>
     <row r="1762">
       <c r="A1762" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1762" t="n">
-        <v>23880</v>
+        <v>5642</v>
       </c>
       <c r="C1762" t="n">
         <v>1.25999999046326</v>
       </c>
       <c r="D1762" t="n">
-        <v>1.22000002861023</v>
+        <v>1.24000000953674</v>
       </c>
       <c r="E1762" t="n">
-        <v>1.23500001430511</v>
+        <v>1.25</v>
       </c>
       <c r="F1762" t="n">
         <v>1.24000000953674</v>
@@ -40900,22 +40900,22 @@
     </row>
     <row r="1763">
       <c r="A1763" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1763" t="n">
-        <v>20010</v>
+        <v>23880</v>
       </c>
       <c r="C1763" t="n">
-        <v>1.25</v>
+        <v>1.25999999046326</v>
       </c>
       <c r="D1763" t="n">
-        <v>1.19000005722046</v>
+        <v>1.22000002861023</v>
       </c>
       <c r="E1763" t="n">
-        <v>1.25</v>
+        <v>1.23500001430511</v>
       </c>
       <c r="F1763" t="n">
-        <v>1.21000003814697</v>
+        <v>1.24000000953674</v>
       </c>
       <c r="G1763" t="s">
         <v>7</v>
@@ -40923,19 +40923,19 @@
     </row>
     <row r="1764">
       <c r="A1764" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1764" t="n">
-        <v>33260</v>
+        <v>20010</v>
       </c>
       <c r="C1764" t="n">
-        <v>1.24500000476837</v>
+        <v>1.25</v>
       </c>
       <c r="D1764" t="n">
-        <v>1.16999995708466</v>
+        <v>1.19000005722046</v>
       </c>
       <c r="E1764" t="n">
-        <v>1.23000001907349</v>
+        <v>1.25</v>
       </c>
       <c r="F1764" t="n">
         <v>1.21000003814697</v>
@@ -40946,16 +40946,16 @@
     </row>
     <row r="1765">
       <c r="A1765" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1765" t="n">
-        <v>26231</v>
+        <v>33260</v>
       </c>
       <c r="C1765" t="n">
         <v>1.24500000476837</v>
       </c>
       <c r="D1765" t="n">
-        <v>1.17999994754791</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="E1765" t="n">
         <v>1.23000001907349</v>
@@ -40969,24 +40969,47 @@
     </row>
     <row r="1766">
       <c r="A1766" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1766" t="n">
-        <v>10015</v>
+        <v>26231</v>
       </c>
       <c r="C1766" t="n">
+        <v>1.24500000476837</v>
+      </c>
+      <c r="D1766" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="E1766" t="n">
         <v>1.23000001907349</v>
       </c>
-      <c r="D1766" t="n">
+      <c r="F1766" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G1766" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1767" t="n">
+        <v>10147</v>
+      </c>
+      <c r="C1767" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="D1767" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="E1767" t="n">
         <v>1.20500004291534</v>
       </c>
-      <c r="E1766" t="n">
-        <v>1.20500004291534</v>
-      </c>
-      <c r="F1766" t="n">
-        <v>1.23500001430511</v>
-      </c>
-      <c r="G1766" t="s">
+      <c r="F1767" t="n">
+        <v>1.22500002384186</v>
+      </c>
+      <c r="G1767" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -46369,6 +46369,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1770">
+      <c r="A1770" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1770" t="n">
+        <v>3050</v>
+      </c>
+      <c r="C1770" t="n">
+        <v>1.2150000333786</v>
+      </c>
+      <c r="D1770" t="n">
+        <v>1.18499994277954</v>
+      </c>
+      <c r="E1770" t="n">
+        <v>1.19500005245209</v>
+      </c>
+      <c r="F1770" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G1770" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="H1770" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -46395,6 +46395,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1771">
+      <c r="A1771" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1771" t="n">
+        <v>59457</v>
+      </c>
+      <c r="C1771" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="D1771" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="E1771" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="F1771" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="G1771" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="H1771" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -46403,7 +46403,7 @@
         <v>59457</v>
       </c>
       <c r="C1771" t="n">
-        <v>1.21000003814697</v>
+        <v>1.22000002861023</v>
       </c>
       <c r="D1771" t="n">
         <v>1.19000005722046</v>
@@ -46418,6 +46418,32 @@
         <v>1.22000002861023</v>
       </c>
       <c r="H1771" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1772" t="n">
+        <v>13429</v>
+      </c>
+      <c r="C1772" t="n">
+        <v>1.2150000333786</v>
+      </c>
+      <c r="D1772" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="E1772" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="F1772" t="n">
+        <v>1.2150000333786</v>
+      </c>
+      <c r="G1772" t="n">
+        <v>1.2150000333786</v>
+      </c>
+      <c r="H1772" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -46447,6 +46447,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1773">
+      <c r="A1773" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1773" t="n">
+        <v>3251</v>
+      </c>
+      <c r="C1773" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="D1773" t="n">
+        <v>1.2150000333786</v>
+      </c>
+      <c r="E1773" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="F1773" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="G1773" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="H1773" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -46525,6 +46525,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1776">
+      <c r="A1776" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1776" t="n">
+        <v>22620</v>
+      </c>
+      <c r="C1776" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="D1776" t="n">
+        <v>1.15499997138977</v>
+      </c>
+      <c r="E1776" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="F1776" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="G1776" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="H1776" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -41282,8 +41282,31 @@
       <c r="E1779" t="n">
         <v>1.16499996185303</v>
       </c>
-      <c r="F1779"/>
+      <c r="F1779" t="n">
+        <v>1.14999997615814</v>
+      </c>
       <c r="G1779" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1780" t="n">
+        <v>10898</v>
+      </c>
+      <c r="C1780" t="n">
+        <v>1.16499996185303</v>
+      </c>
+      <c r="D1780" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="E1780" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F1780"/>
+      <c r="G1780" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -41305,8 +41305,31 @@
       <c r="E1780" t="n">
         <v>1.1599999666214</v>
       </c>
-      <c r="F1780"/>
+      <c r="F1780" t="n">
+        <v>1.1599999666214</v>
+      </c>
       <c r="G1780" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1781" t="n">
+        <v>34510</v>
+      </c>
+      <c r="C1781" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="D1781" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="E1781" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="F1781"/>
+      <c r="G1781" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -41328,8 +41328,31 @@
       <c r="E1781" t="n">
         <v>1.13999998569489</v>
       </c>
-      <c r="F1781"/>
+      <c r="F1781" t="n">
+        <v>1.19000005722046</v>
+      </c>
       <c r="G1781" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1782" t="n">
+        <v>87098</v>
+      </c>
+      <c r="C1782" t="n">
+        <v>1.23500001430511</v>
+      </c>
+      <c r="D1782" t="n">
+        <v>1.15499997138977</v>
+      </c>
+      <c r="E1782" t="n">
+        <v>1.18499994277954</v>
+      </c>
+      <c r="F1782"/>
+      <c r="G1782" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -41351,8 +41351,31 @@
       <c r="E1782" t="n">
         <v>1.18499994277954</v>
       </c>
-      <c r="F1782"/>
+      <c r="F1782" t="n">
+        <v>1.23000001907349</v>
+      </c>
       <c r="G1782" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1783" t="n">
+        <v>475869</v>
+      </c>
+      <c r="C1783" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="D1783" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="E1783" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="F1783"/>
+      <c r="G1783" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -41381,6 +41381,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1784">
+      <c r="A1784" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1784" t="n">
+        <v>84740</v>
+      </c>
+      <c r="C1784" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="D1784" t="n">
+        <v>1.25499999523163</v>
+      </c>
+      <c r="E1784" t="n">
+        <v>1.25999999046326</v>
+      </c>
+      <c r="F1784" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="G1784" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -46811,6 +46811,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1787">
+      <c r="A1787" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1787" t="n">
+        <v>44061</v>
+      </c>
+      <c r="C1787" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D1787" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E1787" t="n">
+        <v>1.2849999666214</v>
+      </c>
+      <c r="F1787" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="G1787" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="H1787" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -46822,7 +46822,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="D1787" t="n">
-        <v>1.25</v>
+        <v>1.24500000476837</v>
       </c>
       <c r="E1787" t="n">
         <v>1.2849999666214</v>
@@ -46834,6 +46834,32 @@
         <v>1.26999998092651</v>
       </c>
       <c r="H1787" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1788" t="n">
+        <v>33656</v>
+      </c>
+      <c r="C1788" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="D1788" t="n">
+        <v>1.22500002384186</v>
+      </c>
+      <c r="E1788" t="n">
+        <v>1.27499997615814</v>
+      </c>
+      <c r="F1788" t="n">
+        <v>1.27999997138977</v>
+      </c>
+      <c r="G1788" t="n">
+        <v>1.27999997138977</v>
+      </c>
+      <c r="H1788" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -52259,6 +52259,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1790">
+      <c r="A1790" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1790" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1790" t="n">
+        <v>1.27499997615814</v>
+      </c>
+      <c r="D1790" t="n">
+        <v>1.27999997138977</v>
+      </c>
+      <c r="E1790" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="F1790" t="n">
+        <v>1.25499999523163</v>
+      </c>
+      <c r="G1790" t="n">
+        <v>1.25499999523163</v>
+      </c>
+      <c r="H1790" t="n">
+        <v>49796</v>
+      </c>
+      <c r="I1790" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -52288,6 +52288,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1791">
+      <c r="A1791" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1791" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1791" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="D1791" t="n">
+        <v>1.27999997138977</v>
+      </c>
+      <c r="E1791" t="n">
+        <v>1.25499999523163</v>
+      </c>
+      <c r="F1791" t="n">
+        <v>1.25499999523163</v>
+      </c>
+      <c r="G1791" t="n">
+        <v>1.25499999523163</v>
+      </c>
+      <c r="H1791" t="n">
+        <v>38868</v>
+      </c>
+      <c r="I1791" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -52317,6 +52317,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1792">
+      <c r="A1792" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1792" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1792" t="n">
+        <v>1.22500002384186</v>
+      </c>
+      <c r="D1792" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="E1792" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="F1792" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="G1792" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="H1792" t="n">
+        <v>27077</v>
+      </c>
+      <c r="I1792" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -52346,6 +52346,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1793">
+      <c r="A1793" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1793" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1793" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D1793" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E1793" t="n">
+        <v>1.19500005245209</v>
+      </c>
+      <c r="F1793" t="n">
+        <v>1.24500000476837</v>
+      </c>
+      <c r="G1793" t="n">
+        <v>1.24500000476837</v>
+      </c>
+      <c r="H1793" t="n">
+        <v>20177</v>
+      </c>
+      <c r="I1793" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -52369,9 +52369,38 @@
         <v>1.24500000476837</v>
       </c>
       <c r="H1793" t="n">
-        <v>20177</v>
+        <v>20577</v>
       </c>
       <c r="I1793" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1794" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1794" t="n">
+        <v>1.26499998569489</v>
+      </c>
+      <c r="D1794" t="n">
+        <v>1.26499998569489</v>
+      </c>
+      <c r="E1794" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="F1794" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="G1794" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="H1794" t="n">
+        <v>17087</v>
+      </c>
+      <c r="I1794" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -52404,6 +52404,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1795">
+      <c r="A1795" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1795" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1795" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="D1795" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E1795" t="n">
+        <v>1.20500004291534</v>
+      </c>
+      <c r="F1795" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="G1795" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="H1795" t="n">
+        <v>72708</v>
+      </c>
+      <c r="I1795" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -52433,6 +52433,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1796">
+      <c r="A1796" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1796" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1796" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="D1796" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="E1796" t="n">
+        <v>1.16499996185303</v>
+      </c>
+      <c r="F1796" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="G1796" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="H1796" t="n">
+        <v>53119</v>
+      </c>
+      <c r="I1796" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -52462,6 +52462,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1797">
+      <c r="A1797" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1797" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1797" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="D1797" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="E1797" t="n">
+        <v>1.16499996185303</v>
+      </c>
+      <c r="F1797" t="n">
+        <v>1.20500004291534</v>
+      </c>
+      <c r="G1797" t="n">
+        <v>1.20500004291534</v>
+      </c>
+      <c r="H1797" t="n">
+        <v>33672</v>
+      </c>
+      <c r="I1797" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CYB.MI.xlsx
+++ b/data/CYB.MI.xlsx
@@ -52491,6 +52491,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1798">
+      <c r="A1798" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1798" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1798" t="n">
+        <v>1.20500004291534</v>
+      </c>
+      <c r="D1798" t="n">
+        <v>1.20500004291534</v>
+      </c>
+      <c r="E1798" t="n">
+        <v>1.16499996185303</v>
+      </c>
+      <c r="F1798" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="G1798" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="H1798" t="n">
+        <v>23263</v>
+      </c>
+      <c r="I1798" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
